--- a/artfynd/A 22567-2025 artfynd.xlsx
+++ b/artfynd/A 22567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121151041</v>
       </c>
       <c r="B2" t="n">
-        <v>90207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151040</v>
+        <v>121152781</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>744548</v>
+        <v>744646</v>
       </c>
       <c r="R3" t="n">
-        <v>7320184</v>
+        <v>7320230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,6 +884,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121151040</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vitberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>744548</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7320184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22567-2025 artfynd.xlsx
+++ b/artfynd/A 22567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152781</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121151040</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>